--- a/ML_SSW_2025/Analysis_ML_Data.xlsx
+++ b/ML_SSW_2025/Analysis_ML_Data.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pablo\Desktop\ML_SSW\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pablo\Desktop\InvestigacionUSFQ\SSWCompleteAnalysis\SingleSolitaryWaveAnalysis\ML_SSW_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C48F1D-EE23-448F-8878-C1E6DDD75E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA80105-062F-4B38-AE8E-CB5EEAED542C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{AA4ED9E8-B08C-461E-9CA5-C3521FC84154}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{AA4ED9E8-B08C-461E-9CA5-C3521FC84154}"/>
   </bookViews>
   <sheets>
     <sheet name="Original Data" sheetId="1" r:id="rId1"/>
     <sheet name="ML_Example" sheetId="2" r:id="rId2"/>
     <sheet name="ML_TrainingData" sheetId="3" r:id="rId3"/>
+    <sheet name="ML_TestData_Ceramica" sheetId="4" r:id="rId4"/>
+    <sheet name="Ajuste_K" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="67">
   <si>
     <t>F1</t>
   </si>
@@ -146,6 +148,99 @@
   </si>
   <si>
     <t>C</t>
+  </si>
+  <si>
+    <t>Probeta</t>
+  </si>
+  <si>
+    <t>Energía</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Golpes</t>
+  </si>
+  <si>
+    <t>M1 - Mod</t>
+  </si>
+  <si>
+    <t>M2 - Mod</t>
+  </si>
+  <si>
+    <t>M3 - Mod</t>
+  </si>
+  <si>
+    <t>M1 - Est</t>
+  </si>
+  <si>
+    <t>M2 - Est</t>
+  </si>
+  <si>
+    <t>M3 - Est</t>
+  </si>
+  <si>
+    <t>M4 - Est</t>
+  </si>
+  <si>
+    <t>M4 - Mod</t>
+  </si>
+  <si>
+    <t>M5 - Mod</t>
+  </si>
+  <si>
+    <t>M6 - Mod</t>
+  </si>
+  <si>
+    <t>M5 - Est</t>
+  </si>
+  <si>
+    <t>M6 - Est</t>
+  </si>
+  <si>
+    <t>TOF Prom</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>Den. Seca</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>g/cm3</t>
+  </si>
+  <si>
+    <t>25 golpes mod</t>
+  </si>
+  <si>
+    <t>MAX</t>
+  </si>
+  <si>
+    <t>DENSIDAD</t>
+  </si>
+  <si>
+    <t>56 golpes mod</t>
+  </si>
+  <si>
+    <t>25 golpes standard</t>
+  </si>
+  <si>
+    <t>Datos Matlab 0.1</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>Datos Matlab 0.3</t>
+  </si>
+  <si>
+    <t>Datos Matlab 0.5</t>
   </si>
 </sst>
 </file>
@@ -156,7 +251,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -181,8 +276,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="4"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -207,8 +327,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -240,13 +372,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -281,6 +426,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2985,4 +3140,973 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B6664A1-1E84-4EEF-A331-E575C33F569C}">
+  <dimension ref="A1:R21"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="16384" width="9.06640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="1">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.13911993692717059</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1.6982865896324033</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.6584291622044007</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.11843409316154611</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="1">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1.7749999999999999</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.763728134637909</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.11805225653206648</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" s="2">
+        <v>25</v>
+      </c>
+      <c r="M3" s="1">
+        <v>1.3520135201360978E-3</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0.11843409316154611</v>
+      </c>
+      <c r="O3" s="1">
+        <v>1.6584291622044007</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="R3" s="1">
+        <v>0.13911993692717059</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1.7749999999999999</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.6822689096024417</v>
+      </c>
+      <c r="H4" s="1">
+        <v>9.6678107984795758E-2</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L4" s="2">
+        <v>56</v>
+      </c>
+      <c r="M4" s="1">
+        <v>1.3180131801320259E-3</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0.11805225653206648</v>
+      </c>
+      <c r="O4" s="1">
+        <v>1.763728134637909</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="R4" s="1">
+        <v>1.6982865896324033</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1.7749999999999999</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.6483733962172045</v>
+      </c>
+      <c r="H5" s="1">
+        <v>8.0713111267325499E-2</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" s="2">
+        <v>56</v>
+      </c>
+      <c r="M5" s="1">
+        <v>1.2780127801285319E-3</v>
+      </c>
+      <c r="N5" s="1">
+        <v>9.6678107984795758E-2</v>
+      </c>
+      <c r="O5" s="1">
+        <v>1.6822689096024417</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1.62</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.480677915463195</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0.11589041095890402</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L6" s="2">
+        <v>56</v>
+      </c>
+      <c r="M6" s="1">
+        <v>1.2380123801243302E-3</v>
+      </c>
+      <c r="N6" s="1">
+        <v>8.0713111267325499E-2</v>
+      </c>
+      <c r="O6" s="1">
+        <v>1.6483733962172045</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1.62</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1.4904689597154233</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.13460442691211932</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" s="2">
+        <v>25</v>
+      </c>
+      <c r="M7" s="1">
+        <v>1.8960189601884298E-3</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0.11589041095890402</v>
+      </c>
+      <c r="O7" s="1">
+        <v>1.480677915463195</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1.62</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1.5294344523239138</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0.14028029887536533</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L8" s="2">
+        <v>25</v>
+      </c>
+      <c r="M8" s="1">
+        <v>1.83601836018994E-3</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0.13460442691211932</v>
+      </c>
+      <c r="O8" s="1">
+        <v>1.4904689597154233</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="R8" s="1">
+        <v>0.13300000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1.62</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1.5475074537777984</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0.15156950672645753</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L9" s="2">
+        <v>25</v>
+      </c>
+      <c r="M9" s="1">
+        <v>1.4240142401433782E-3</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0.14028029887536533</v>
+      </c>
+      <c r="O9" s="1">
+        <v>1.5294344523239138</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="R9" s="1">
+        <v>1.7749999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="1">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1.7749999999999999</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1.7772421994397172</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.1430861723446894</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L10" s="2">
+        <v>25</v>
+      </c>
+      <c r="M10" s="1">
+        <v>1.6520165201640679E-3</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0.15156950672645753</v>
+      </c>
+      <c r="O10" s="1">
+        <v>1.5475074537777984</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="1">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1.7749999999999999</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1.6951263354634258</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0.17279256442754556</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="1">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1.7749999999999999</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1.6321784584194605</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0.1863437537080784</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1.62</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1.6090048691339709</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0.16556028504471754</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="L13" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="R13" s="1">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1.62</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1.6060302554528956</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0.19470446643487566</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L14" s="2">
+        <v>56</v>
+      </c>
+      <c r="M14" s="1">
+        <v>1.3240132401346459E-3</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0.1430861723446894</v>
+      </c>
+      <c r="O14" s="1">
+        <v>1.7772421994397172</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="R14" s="1">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="1">
+        <v>2</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0.13911993692717059</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1.6982865896324033</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1.6867190368361413</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0.13297332509443671</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L15" s="2">
+        <v>56</v>
+      </c>
+      <c r="M15" s="1">
+        <v>1.484014840148264E-3</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0.17279256442754556</v>
+      </c>
+      <c r="O15" s="1">
+        <v>1.6951263354634258</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="1">
+        <v>2</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0.13911993692717059</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1.6982865896324033</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1.678484887889131</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0.15578764142732804</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="2">
+        <v>56</v>
+      </c>
+      <c r="M16" s="1">
+        <v>1.5760157601505359E-3</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0.1863437537080784</v>
+      </c>
+      <c r="O16" s="1">
+        <v>1.6321784584194605</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0.13911993692717059</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1.6982865896324033</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1.601954608561813</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0.16935064935064942</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L17" s="2">
+        <v>25</v>
+      </c>
+      <c r="M17" s="1">
+        <v>1.686016860168494E-3</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0.16556028504471754</v>
+      </c>
+      <c r="O17" s="1">
+        <v>1.6090048691339709</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="K18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L18" s="2">
+        <v>25</v>
+      </c>
+      <c r="M18" s="1">
+        <v>1.9700197001942142E-3</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0.19470446643487566</v>
+      </c>
+      <c r="O18" s="1">
+        <v>1.6060302554528956</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="K19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L19" s="2">
+        <v>25</v>
+      </c>
+      <c r="M19" s="1">
+        <v>1.4060140601390699E-3</v>
+      </c>
+      <c r="N19" s="1">
+        <v>0.13297332509443671</v>
+      </c>
+      <c r="O19" s="1">
+        <v>1.6867190368361413</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="K20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L20" s="2">
+        <v>25</v>
+      </c>
+      <c r="M20" s="1">
+        <v>1.516015160152762E-3</v>
+      </c>
+      <c r="N20" s="1">
+        <v>0.15578764142732804</v>
+      </c>
+      <c r="O20" s="1">
+        <v>1.678484887889131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="K21" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L21" s="2">
+        <v>25</v>
+      </c>
+      <c r="M21" s="1">
+        <v>1.455014550145075E-3</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0.16935064935064942</v>
+      </c>
+      <c r="O21" s="1">
+        <v>1.601954608561813</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDBDB9C2-512F-468A-9E95-0283D0C33914}">
+  <dimension ref="B2:C33"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="2" spans="2:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="B2" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="18"/>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B3" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B4" s="6">
+        <v>10000000</v>
+      </c>
+      <c r="C4" s="6">
+        <v>1.4007381733822328</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B5" s="6">
+        <v>40000000</v>
+      </c>
+      <c r="C5" s="6">
+        <v>1.2140668286409155</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B6" s="6">
+        <v>100000000</v>
+      </c>
+      <c r="C6" s="6">
+        <v>1.1177048296059127</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B7" s="6">
+        <v>200000000</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1.0909213561826436</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B8" s="6">
+        <v>300000000</v>
+      </c>
+      <c r="C8" s="6">
+        <v>1.08058437749855</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B9" s="6">
+        <v>500000000</v>
+      </c>
+      <c r="C9" s="6">
+        <v>1.0723113034395499</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B10" s="6">
+        <v>700000000</v>
+      </c>
+      <c r="C10" s="6">
+        <v>1.0694334868948585</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B11" s="6">
+        <v>1000000000</v>
+      </c>
+      <c r="C11" s="6">
+        <v>1.0629208338167233</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+    </row>
+    <row r="13" spans="2:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="B13" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="18"/>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B14" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B15" s="6">
+        <v>10000000</v>
+      </c>
+      <c r="C15" s="6">
+        <v>1.3259736795022041</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B16" s="6">
+        <v>40000000</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1.1531017802399695</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B17" s="6">
+        <v>100000000</v>
+      </c>
+      <c r="C17" s="6">
+        <v>1.0821813204036701</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B18" s="6">
+        <v>200000000</v>
+      </c>
+      <c r="C18" s="6">
+        <v>1.05394888195359</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B19" s="6">
+        <v>300000000</v>
+      </c>
+      <c r="C19" s="6">
+        <v>1.0434829598242401</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B20" s="6">
+        <v>500000000</v>
+      </c>
+      <c r="C20" s="6">
+        <v>1.0350255733857601</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B21" s="6">
+        <v>700000000</v>
+      </c>
+      <c r="C21" s="6">
+        <v>1.0306193761935976</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B22" s="6">
+        <v>1000000000</v>
+      </c>
+      <c r="C22" s="6">
+        <v>1.0245285302824279</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+    </row>
+    <row r="24" spans="2:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="B24" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="18"/>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B25" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B26" s="6">
+        <v>10000000</v>
+      </c>
+      <c r="C26" s="6">
+        <v>1.2535678601649396</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B27" s="6">
+        <v>40000000</v>
+      </c>
+      <c r="C27" s="6">
+        <v>1.0971579631994441</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B28" s="6">
+        <v>100000000</v>
+      </c>
+      <c r="C28" s="6">
+        <v>1.0400670315095699</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B29" s="6">
+        <v>200000000</v>
+      </c>
+      <c r="C29" s="6">
+        <v>1.0169791360217704</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B30" s="6">
+        <v>300000000</v>
+      </c>
+      <c r="C30" s="6">
+        <v>1.00942182278415</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B31" s="6">
+        <v>500000000</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.99776030496475798</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B32" s="6">
+        <v>700000000</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.98765618756805007</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B33" s="6">
+        <v>1000000000</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.97950536977613056</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B24:C24"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/ML_SSW_2025/Analysis_ML_Data.xlsx
+++ b/ML_SSW_2025/Analysis_ML_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pablo\Desktop\InvestigacionUSFQ\SSWCompleteAnalysis\SingleSolitaryWaveAnalysis\ML_SSW_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA80105-062F-4B38-AE8E-CB5EEAED542C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B9F313-7102-4362-8A17-9AE1F3786964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{AA4ED9E8-B08C-461E-9CA5-C3521FC84154}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="43">
   <si>
     <t>F1</t>
   </si>
@@ -150,84 +150,6 @@
     <t>C</t>
   </si>
   <si>
-    <t>Probeta</t>
-  </si>
-  <si>
-    <t>Energía</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Golpes</t>
-  </si>
-  <si>
-    <t>M1 - Mod</t>
-  </si>
-  <si>
-    <t>M2 - Mod</t>
-  </si>
-  <si>
-    <t>M3 - Mod</t>
-  </si>
-  <si>
-    <t>M1 - Est</t>
-  </si>
-  <si>
-    <t>M2 - Est</t>
-  </si>
-  <si>
-    <t>M3 - Est</t>
-  </si>
-  <si>
-    <t>M4 - Est</t>
-  </si>
-  <si>
-    <t>M4 - Mod</t>
-  </si>
-  <si>
-    <t>M5 - Mod</t>
-  </si>
-  <si>
-    <t>M6 - Mod</t>
-  </si>
-  <si>
-    <t>M5 - Est</t>
-  </si>
-  <si>
-    <t>M6 - Est</t>
-  </si>
-  <si>
-    <t>TOF Prom</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>Den. Seca</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>g/cm3</t>
-  </si>
-  <si>
-    <t>25 golpes mod</t>
-  </si>
-  <si>
-    <t>MAX</t>
-  </si>
-  <si>
-    <t>DENSIDAD</t>
-  </si>
-  <si>
-    <t>56 golpes mod</t>
-  </si>
-  <si>
-    <t>25 golpes standard</t>
-  </si>
-  <si>
     <t>Datos Matlab 0.1</t>
   </si>
   <si>
@@ -242,6 +164,12 @@
   <si>
     <t>Datos Matlab 0.5</t>
   </si>
+  <si>
+    <t>Arcilla</t>
+  </si>
+  <si>
+    <t>Limo</t>
+  </si>
 </sst>
 </file>
 
@@ -251,7 +179,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,30 +207,13 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color theme="4"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -329,18 +240,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -372,26 +277,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -412,11 +304,7 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -426,16 +314,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,6 +341,1790 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Ajuste_K!$B$4:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>10000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>40000000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100000000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>200000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>300000000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500000000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>700000000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1000000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Ajuste_K!$C$4:$C$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1.4007381733822328</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.2140668286409155</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.1177048296059127</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0909213561826436</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.08058437749855</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.0723113034395499</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.0694334868948585</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0629208338167233</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-94B9-4F06-8062-CD5936D05C8A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1692211952"/>
+        <c:axId val="1692212432"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1692211952"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1692212432"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1692212432"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1692211952"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Ajuste_K!$B$15:$B$22</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>10000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>40000000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100000000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>200000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>300000000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500000000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>700000000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1000000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Ajuste_K!$C$15:$C$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1.3259736795022041</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1531017802399695</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0821813204036701</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.05394888195359</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0434829598242401</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.0350255733857601</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.0306193761935976</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0245285302824279</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7AF4-41BC-A5A4-3AF17170A2D1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1692211952"/>
+        <c:axId val="1692212432"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1692211952"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1692212432"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1692212432"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1692211952"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -625,6 +2297,85 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>321467</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>38099</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>28574</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76735AA6-EB63-D84F-6E79-BAB760A7DE9F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>300037</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>71438</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>588170</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>61913</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D77483B2-1C06-48B4-B616-37E2252FE289}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1540,18 +3291,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="15"/>
-      <c r="K1" s="13" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="11"/>
+      <c r="K1" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="13"/>
+      <c r="L1" s="9"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
@@ -1958,1184 +3709,1204 @@
   <dimension ref="A1:R40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="10" max="10" width="14.3984375" customWidth="1"/>
+    <col min="1" max="9" width="9.06640625" style="1"/>
+    <col min="10" max="10" width="14.3984375" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.06640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>1</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>2.5312994394433002E-3</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>2.2503547032552462</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>0.112</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>1.9650000000000001</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>1.8947397051669903</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>7.6316350458324425E-2</v>
       </c>
+      <c r="J2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>1.9180062110610407E-3</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>2.4880971669127279</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>0.112</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>1.9650000000000001</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>1.9348444370707474</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>9.6030729833546741E-2</v>
       </c>
+      <c r="J3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>1</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>2.1328541573080173E-3</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>2.8686591440287219</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>0.112</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>1.9650000000000001</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>1.9660781433873795</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>0.11954206602768888</v>
       </c>
+      <c r="J4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>2.6328639231230967E-3</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>2.7353389242681727</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>0.112</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>1.9650000000000001</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>1.9576916183018995</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>0.13162271323354713</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>2.0547276313990894E-3</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>2.8555746377458924</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>0.112</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>1.9650000000000001</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>1.8960009900803738</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>0.14385679414157856</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>2</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>1.6094064337182524E-3</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>2.1523322493313732</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>9.4E-2</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>2.0649999999999999</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>2.016690673287997</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>5.7142857142856933E-2</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>2</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>1.3515888982202461E-3</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>2.1072494854759722</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>9.4E-2</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>2.0649999999999999</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>2.0460168732495467</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>6.9455103607060725E-2</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>2</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>1.3125256352669369E-3</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>2.1101041475104605</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>9.4E-2</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>2.0649999999999999</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>2.054876802148133</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>9.3951093951094009E-2</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <v>2</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>2.2891072091269392E-3</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>3.8861468513426241</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>9.4E-2</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>2.0649999999999999</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>2.0561458679914573</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>0.10994263862332682</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1">
         <v>2</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>2.7227094279185238E-3</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>2.7517605314138778</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>9.4E-2</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>2.0649999999999999</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>1.9724273059498865</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>0.13374411018484977</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="1">
         <v>3</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>2.1914490517382034E-3</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>2.04169089639701</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>8.0500000000000002E-2</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>2.1349999999999998</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>2.0788260713467381</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>4.5409015025041716E-2</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="1">
         <v>3</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>1.5469052129907014E-3</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>1.98166056362473</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>8.0500000000000002E-2</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>2.1349999999999998</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>2.1232785944132311</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>7.8056951423785534E-2</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
+      <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="1">
         <v>3</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>1.5078419500383689E-3</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>3.3410512935202923</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>8.0500000000000002E-2</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>2.1349999999999998</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>2.1289019997015148</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>9.9105071262843708E-2</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="1">
         <v>3</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>2.2617629250589744E-3</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>2.5145694984763485</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>8.0500000000000002E-2</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>2.1349999999999998</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>2.0642917651773396</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>0.11525518788558609</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="1">
         <v>1</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>1.5273735815121369E-3</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="8">
         <v>2.5650682126413478</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>0.18099999999999999</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>1.67</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>1.6605570810323071</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>0.1622203098106714</v>
       </c>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="9"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="15"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
+      <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="1">
         <v>1</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>2.890681458621547E-3</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="8">
         <v>3.7188004175787275</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>0.18099999999999999</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>1.67</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>1.6615859430054534</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>0.19980314960629944</v>
       </c>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="9"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="15"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
+      <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="1">
         <v>1</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>3.125061036351795E-3</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="8">
         <v>3.3843681758450024</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>0.18099999999999999</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <v>1.67</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>1.5068636991765223</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>0.26691858467880425</v>
       </c>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="9"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="15"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
+      <c r="A19" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="1">
         <v>1</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>1.6015937811292957E-3</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="8">
         <v>2.4957530617775538</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>0.18099999999999999</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>1.67</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>1.5747783227223249</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>0.11699064074874009</v>
       </c>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="9"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="15"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
+      <c r="A20" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="1">
         <v>2</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>1.2695560460160848E-3</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="8">
         <v>2.0158880434200936</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>0.15</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <v>1.7949999999999999</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>1.741579267448629</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>0.10631793478260841</v>
       </c>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="9"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="15"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
+      <c r="A21" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="1">
         <v>2</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="1">
         <v>1.2549073224095153E-3</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="8">
         <v>2.0417622203199088</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>0.15</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <v>1.7949999999999999</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>1.7894306168364227</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>0.14524886877828025</v>
       </c>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="9"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="15"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
+      <c r="A22" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="1">
         <v>2</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="1">
         <v>1.464872360793379E-3</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="8">
         <v>2.0306623489044209</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
         <v>0.15</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="1">
         <v>1.7949999999999999</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>1.8061947339895521</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>0.16490566037735838</v>
       </c>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="9"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="15"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
+      <c r="A23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="1">
         <v>2</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="1">
         <v>1.7773784644233182E-3</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="8">
         <v>2.8830907121228746</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="1">
         <v>0.15</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="1">
         <v>1.7949999999999999</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="1">
         <v>1.5456713004509131</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
         <v>0.22849968612680469</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
+      <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="1">
         <v>3</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="1">
         <v>1.2070548252893331E-3</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="8">
         <v>2.6610701832437287</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="1">
         <v>0.14499999999999999</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="1">
         <v>1.82</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="1">
         <v>1.7743615616875121</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="1">
         <v>9.0436590436590164E-2</v>
       </c>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="9"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="15"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
+      <c r="A25" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="1">
         <v>3</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="1">
         <v>1.101584015313506E-3</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="8">
         <v>2.3321449284662177</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="1">
         <v>0.14499999999999999</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="1">
         <v>1.82</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="1">
         <v>1.8202988531912971</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="1">
         <v>0.1508515815085158</v>
       </c>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="9"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="15"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
+      <c r="A26" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="1">
         <v>3</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="1">
         <v>1.3984648137657985E-3</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="8">
         <v>2.9639171140714216</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="1">
         <v>0.14499999999999999</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="1">
         <v>1.82</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="1">
         <v>1.7636738086928547</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="1">
         <v>0.18550811785929003</v>
       </c>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="9"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="15"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
+      <c r="A27" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="1">
         <v>3</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="1">
         <v>2.3008261880093526E-3</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="8">
         <v>4.120947298491358</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="1">
         <v>0.14499999999999999</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="1">
         <v>1.82</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="1">
         <v>1.642825029593429</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="1">
         <v>0.22477693891557984</v>
       </c>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="9"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="15"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
+      <c r="A28" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="1">
         <v>1</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="1">
         <v>1.8476923377406251E-3</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="8">
         <v>1.9246707861364016</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="1">
         <v>0.21</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="1">
         <v>1.54</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="1">
         <v>1.371360301675431</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="1">
         <v>0.11302982731554165</v>
       </c>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="8"/>
-      <c r="O28" s="10"/>
-      <c r="P28" s="10"/>
-      <c r="Q28" s="12"/>
-      <c r="R28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="17"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="8"/>
+      <c r="Q28" s="16"/>
+      <c r="R28" s="17"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
+      <c r="A29" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="1">
         <v>1</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="1">
         <v>1.7318046576407415E-3</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="8">
         <v>2.4186860629867977</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="1">
         <v>0.21</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="1">
         <v>1.54</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="1">
         <v>1.4537727083051852</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="1">
         <v>0.14261363636363625</v>
       </c>
-      <c r="M29" s="8"/>
-      <c r="O29" s="10"/>
-      <c r="P29" s="10"/>
-      <c r="Q29" s="12"/>
-      <c r="R29" s="8"/>
+      <c r="M29" s="17"/>
+      <c r="O29" s="8"/>
+      <c r="P29" s="8"/>
+      <c r="Q29" s="16"/>
+      <c r="R29" s="17"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
+      <c r="A30" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="1">
         <v>1</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="1">
         <v>1.6601886755722717E-3</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="8">
         <v>2.0687647764526438</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="1">
         <v>0.21</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="1">
         <v>1.54</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="1">
         <v>1.5161625901741522</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="1">
         <v>0.19204244031830223</v>
       </c>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="8"/>
-      <c r="O30" s="10"/>
-      <c r="P30" s="10"/>
-      <c r="Q30" s="12"/>
-      <c r="R30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="16"/>
+      <c r="M30" s="17"/>
+      <c r="O30" s="8"/>
+      <c r="P30" s="8"/>
+      <c r="Q30" s="16"/>
+      <c r="R30" s="17"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
+      <c r="A31" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="1">
         <v>1</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="1">
         <v>2.656301880895029E-3</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="8">
         <v>2.4976795945113945</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="1">
         <v>0.21</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="1">
         <v>1.54</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="1">
         <v>1.5264483299970262</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="1">
         <v>0.24606215410813118</v>
       </c>
-      <c r="M31" s="8"/>
-      <c r="O31" s="10"/>
-      <c r="P31" s="10"/>
-      <c r="Q31" s="12"/>
-      <c r="R31" s="8"/>
+      <c r="M31" s="17"/>
+      <c r="O31" s="8"/>
+      <c r="P31" s="8"/>
+      <c r="Q31" s="16"/>
+      <c r="R31" s="17"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
+      <c r="A32" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="1">
         <v>1</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="1">
         <v>3.093810425986021E-3</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="8">
         <v>3.3365380274156862</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="1">
         <v>0.21</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="1">
         <v>1.54</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="1">
         <v>1.3723113437156407</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="1">
         <v>0.29512735326688799</v>
       </c>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="8"/>
-      <c r="O32" s="10"/>
-      <c r="P32" s="10"/>
-      <c r="Q32" s="12"/>
-      <c r="R32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="16"/>
+      <c r="M32" s="17"/>
+      <c r="O32" s="8"/>
+      <c r="P32" s="8"/>
+      <c r="Q32" s="16"/>
+      <c r="R32" s="17"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
+      <c r="A33" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="1">
         <v>2</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="1">
         <v>1.6211254126045442E-3</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="8">
         <v>2.2330826000547201</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="1">
         <v>0.17199999999999999</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="1">
         <v>1.665</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="1">
         <v>1.5620971263646288</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="1">
         <v>0.11079723791588189</v>
       </c>
-      <c r="M33" s="8"/>
-      <c r="O33" s="10"/>
-      <c r="P33" s="10"/>
-      <c r="Q33" s="12"/>
-      <c r="R33" s="8"/>
+      <c r="M33" s="17"/>
+      <c r="O33" s="8"/>
+      <c r="P33" s="8"/>
+      <c r="Q33" s="16"/>
+      <c r="R33" s="17"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
+      <c r="A34" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="1">
         <v>2</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="1">
         <v>1.5820621496551723E-3</v>
       </c>
-      <c r="D34" s="10">
+      <c r="D34" s="8">
         <v>2.2073593865390193</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="1">
         <v>0.17199999999999999</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="1">
         <v>1.665</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="1">
         <v>1.6528849879326786</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="1">
         <v>0.16014588859416429</v>
       </c>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="8"/>
-      <c r="O34" s="10"/>
-      <c r="P34" s="10"/>
-      <c r="Q34" s="12"/>
-      <c r="R34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="16"/>
+      <c r="M34" s="17"/>
+      <c r="O34" s="8"/>
+      <c r="P34" s="8"/>
+      <c r="Q34" s="16"/>
+      <c r="R34" s="17"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
+      <c r="A35" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="1">
         <v>2</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="1">
         <v>1.7422215277640874E-3</v>
       </c>
-      <c r="D35" s="10">
+      <c r="D35" s="8">
         <v>2.2364037902679628</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="1">
         <v>0.17199999999999999</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="1">
         <v>1.665</v>
       </c>
-      <c r="G35">
+      <c r="G35" s="1">
         <v>1.6642190869949036</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="1">
         <v>0.18882395909422914</v>
       </c>
-      <c r="M35" s="8"/>
-      <c r="O35" s="10"/>
-      <c r="P35" s="10"/>
-      <c r="Q35" s="12"/>
-      <c r="R35" s="8"/>
+      <c r="M35" s="17"/>
+      <c r="O35" s="8"/>
+      <c r="P35" s="8"/>
+      <c r="Q35" s="16"/>
+      <c r="R35" s="17"/>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
+      <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="1">
         <v>2</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="1">
         <v>2.5625500498065888E-3</v>
       </c>
-      <c r="D36" s="10">
+      <c r="D36" s="8">
         <v>3.4764804908428872</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="1">
         <v>0.17199999999999999</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="1">
         <v>1.665</v>
       </c>
-      <c r="G36">
+      <c r="G36" s="1">
         <v>1.516311109759529</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="1">
         <v>0.24161849710982658</v>
       </c>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="12"/>
-      <c r="M36" s="8"/>
-      <c r="O36" s="10"/>
-      <c r="P36" s="10"/>
-      <c r="Q36" s="12"/>
-      <c r="R36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="17"/>
+      <c r="O36" s="8"/>
+      <c r="P36" s="8"/>
+      <c r="Q36" s="16"/>
+      <c r="R36" s="17"/>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
+      <c r="A37" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="1">
         <v>3</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="1">
         <v>1.2070548252907543E-3</v>
       </c>
-      <c r="D37" s="10">
+      <c r="D37" s="8">
         <v>2.195333934907997</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="1">
         <v>0.16</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="1">
         <v>1.76</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="1">
         <v>1.7257129651616301</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="1">
         <v>0.13227722772277212</v>
       </c>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="12"/>
-      <c r="M37" s="8"/>
-      <c r="O37" s="10"/>
-      <c r="P37" s="10"/>
-      <c r="Q37" s="12"/>
-      <c r="R37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="16"/>
+      <c r="M37" s="17"/>
+      <c r="O37" s="8"/>
+      <c r="P37" s="8"/>
+      <c r="Q37" s="16"/>
+      <c r="R37" s="17"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
+      <c r="A38" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="1">
         <v>3</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="1">
         <v>1.4414344030157622E-3</v>
       </c>
-      <c r="D38" s="10">
+      <c r="D38" s="8">
         <v>2.3094126654132445</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="1">
         <v>0.16</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="1">
         <v>1.76</v>
       </c>
-      <c r="G38">
+      <c r="G38" s="1">
         <v>1.7591036538600133</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="1">
         <v>0.15978994748687164</v>
       </c>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="12"/>
-      <c r="M38" s="8"/>
-      <c r="O38" s="10"/>
-      <c r="P38" s="10"/>
-      <c r="Q38" s="12"/>
-      <c r="R38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="16"/>
+      <c r="M38" s="17"/>
+      <c r="O38" s="8"/>
+      <c r="P38" s="8"/>
+      <c r="Q38" s="16"/>
+      <c r="R38" s="17"/>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
+      <c r="A39" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="1">
         <v>3</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="1">
         <v>2.027383347330769E-3</v>
       </c>
-      <c r="D39" s="10">
+      <c r="D39" s="8">
         <v>2.3873716925750474</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="1">
         <v>0.16</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="1">
         <v>1.76</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="1">
         <v>1.7091057435408057</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="1">
         <v>0.18811394891944982</v>
       </c>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="12"/>
-      <c r="M39" s="8"/>
-      <c r="O39" s="10"/>
-      <c r="P39" s="10"/>
-      <c r="Q39" s="12"/>
-      <c r="R39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="16"/>
+      <c r="M39" s="17"/>
+      <c r="O39" s="8"/>
+      <c r="P39" s="8"/>
+      <c r="Q39" s="16"/>
+      <c r="R39" s="17"/>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
+      <c r="A40" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="1">
         <v>3</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="1">
         <v>2.3555147561467038E-3</v>
       </c>
-      <c r="D40" s="10">
+      <c r="D40" s="8">
         <v>2.7700167143548673</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="1">
         <v>0.16</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="1">
         <v>1.76</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="1">
         <v>1.5558289053196588</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="1">
         <v>0.22389937106918242</v>
       </c>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="12"/>
-      <c r="M40" s="8"/>
-      <c r="O40" s="10"/>
-      <c r="P40" s="10"/>
-      <c r="Q40" s="12"/>
-      <c r="R40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="17"/>
+      <c r="O40" s="8"/>
+      <c r="P40" s="8"/>
+      <c r="Q40" s="16"/>
+      <c r="R40" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3144,13 +4915,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B6664A1-1E84-4EEF-A331-E575C33F569C}">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="16384" width="9.06640625" style="1"/>
+    <col min="1" max="3" width="9.06640625" style="1"/>
+    <col min="4" max="4" width="9.19921875" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.06640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>29</v>
       </c>
@@ -3175,29 +4948,20 @@
       <c r="H1" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="L1" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" ht="15.75" x14ac:dyDescent="0.5">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
       </c>
+      <c r="C2" s="1">
+        <v>1.3520135201360972E-3</v>
+      </c>
+      <c r="D2" s="1">
+        <v>2.1674065446162127</v>
+      </c>
       <c r="E2" s="1">
         <v>0.13911993692717059</v>
       </c>
@@ -3210,32 +4974,20 @@
       <c r="H2" s="1">
         <v>0.11843409316154611</v>
       </c>
-      <c r="K2" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B3" s="1">
         <v>3</v>
       </c>
+      <c r="C3" s="1">
+        <v>1.3316799834666899E-3</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1.9531749247670491</v>
+      </c>
       <c r="E3" s="1">
         <v>0.13300000000000001</v>
       </c>
@@ -3248,35 +5000,20 @@
       <c r="H3" s="1">
         <v>0.11805225653206648</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="L3" s="2">
-        <v>25</v>
-      </c>
-      <c r="M3" s="1">
-        <v>1.3520135201360978E-3</v>
-      </c>
-      <c r="N3" s="1">
-        <v>0.11843409316154611</v>
-      </c>
-      <c r="O3" s="1">
-        <v>1.6584291622044007</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="R3" s="1">
-        <v>0.13911993692717059</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B4" s="1">
         <v>3</v>
       </c>
+      <c r="C4" s="1">
+        <v>1.2650126501281278E-3</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1.7903215026200612</v>
+      </c>
       <c r="E4" s="1">
         <v>0.13300000000000001</v>
       </c>
@@ -3289,35 +5026,20 @@
       <c r="H4" s="1">
         <v>9.6678107984795758E-2</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4" s="2">
-        <v>56</v>
-      </c>
-      <c r="M4" s="1">
-        <v>1.3180131801320259E-3</v>
-      </c>
-      <c r="N4" s="1">
-        <v>0.11805225653206648</v>
-      </c>
-      <c r="O4" s="1">
-        <v>1.763728134637909</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="R4" s="1">
-        <v>1.6982865896324033</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
       </c>
+      <c r="C5" s="1">
+        <v>1.2375123751242612E-3</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1.9971672054777752</v>
+      </c>
       <c r="E5" s="1">
         <v>0.13300000000000001</v>
       </c>
@@ -3330,29 +5052,20 @@
       <c r="H5" s="1">
         <v>8.0713111267325499E-2</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5" s="2">
-        <v>56</v>
-      </c>
-      <c r="M5" s="1">
-        <v>1.2780127801285319E-3</v>
-      </c>
-      <c r="N5" s="1">
-        <v>9.6678107984795758E-2</v>
-      </c>
-      <c r="O5" s="1">
-        <v>1.6822689096024417</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
+      <c r="C6" s="1">
+        <v>1.8900189001875844E-3</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1.6193108701874659</v>
+      </c>
       <c r="E6" s="1">
         <v>0.18</v>
       </c>
@@ -3365,29 +5078,20 @@
       <c r="H6" s="1">
         <v>0.11589041095890402</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L6" s="2">
-        <v>56</v>
-      </c>
-      <c r="M6" s="1">
-        <v>1.2380123801243302E-3</v>
-      </c>
-      <c r="N6" s="1">
-        <v>8.0713111267325499E-2</v>
-      </c>
-      <c r="O6" s="1">
-        <v>1.6483733962172045</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
+      <c r="C7" s="1">
+        <v>1.8175181751800551E-3</v>
+      </c>
+      <c r="D7" s="1">
+        <v>2.2776304867084574</v>
+      </c>
       <c r="E7" s="1">
         <v>0.18</v>
       </c>
@@ -3400,32 +5104,20 @@
       <c r="H7" s="1">
         <v>0.13460442691211932</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L7" s="2">
-        <v>25</v>
-      </c>
-      <c r="M7" s="1">
-        <v>1.8960189601884298E-3</v>
-      </c>
-      <c r="N7" s="1">
-        <v>0.11589041095890402</v>
-      </c>
-      <c r="O7" s="1">
-        <v>1.480677915463195</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
       </c>
+      <c r="C8" s="1">
+        <v>1.4500145001458502E-3</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1.685209082640706</v>
+      </c>
       <c r="E8" s="1">
         <v>0.18</v>
       </c>
@@ -3438,35 +5130,20 @@
       <c r="H8" s="1">
         <v>0.14028029887536533</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L8" s="2">
-        <v>25</v>
-      </c>
-      <c r="M8" s="1">
-        <v>1.83601836018994E-3</v>
-      </c>
-      <c r="N8" s="1">
-        <v>0.13460442691211932</v>
-      </c>
-      <c r="O8" s="1">
-        <v>1.4904689597154233</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="R8" s="1">
-        <v>0.13300000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
+      <c r="C9" s="1">
+        <v>1.6266829334909971E-3</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1.3945819157578629</v>
+      </c>
       <c r="E9" s="1">
         <v>0.18</v>
       </c>
@@ -3479,35 +5156,20 @@
       <c r="H9" s="1">
         <v>0.15156950672645753</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L9" s="2">
-        <v>25</v>
-      </c>
-      <c r="M9" s="1">
-        <v>1.4240142401433782E-3</v>
-      </c>
-      <c r="N9" s="1">
-        <v>0.14028029887536533</v>
-      </c>
-      <c r="O9" s="1">
-        <v>1.5294344523239138</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="R9" s="1">
-        <v>1.7749999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B10" s="1">
         <v>3</v>
       </c>
+      <c r="C10" s="1">
+        <v>1.3240132401346459E-3</v>
+      </c>
+      <c r="D10" s="1">
+        <v>3.4578189169508007</v>
+      </c>
       <c r="E10" s="1">
         <v>0.13300000000000001</v>
       </c>
@@ -3520,29 +5182,20 @@
       <c r="H10" s="1">
         <v>0.1430861723446894</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L10" s="2">
-        <v>25</v>
-      </c>
-      <c r="M10" s="1">
-        <v>1.6520165201640679E-3</v>
-      </c>
-      <c r="N10" s="1">
-        <v>0.15156950672645753</v>
-      </c>
-      <c r="O10" s="1">
-        <v>1.5475074537777984</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B11" s="1">
         <v>3</v>
       </c>
+      <c r="C11" s="1">
+        <v>1.484014840148264E-3</v>
+      </c>
+      <c r="D11" s="1">
+        <v>3.9803189174894813</v>
+      </c>
       <c r="E11" s="1">
         <v>0.13300000000000001</v>
       </c>
@@ -3556,13 +5209,19 @@
         <v>0.17279256442754556</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B12" s="1">
         <v>3</v>
       </c>
+      <c r="C12" s="1">
+        <v>1.5783491168169423E-3</v>
+      </c>
+      <c r="D12" s="1">
+        <v>3.1502065263277697</v>
+      </c>
       <c r="E12" s="1">
         <v>0.13300000000000001</v>
       </c>
@@ -3575,32 +5234,20 @@
       <c r="H12" s="1">
         <v>0.1863437537080784</v>
       </c>
-      <c r="K12" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="L12" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="15.75" x14ac:dyDescent="0.5">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
       </c>
+      <c r="C13" s="1">
+        <v>1.6860168601684933E-3</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1.9115520166989026</v>
+      </c>
       <c r="E13" s="1">
         <v>0.18</v>
       </c>
@@ -3613,35 +5260,20 @@
       <c r="H13" s="1">
         <v>0.16556028504471754</v>
       </c>
-      <c r="K13" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="L13" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="R13" s="1">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
       </c>
+      <c r="C14" s="1">
+        <v>1.750017500173584E-3</v>
+      </c>
+      <c r="D14" s="1">
+        <v>2.1589852188619298</v>
+      </c>
       <c r="E14" s="1">
         <v>0.18</v>
       </c>
@@ -3654,35 +5286,20 @@
       <c r="H14" s="1">
         <v>0.19470446643487566</v>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="L14" s="2">
-        <v>56</v>
-      </c>
-      <c r="M14" s="1">
-        <v>1.3240132401346459E-3</v>
-      </c>
-      <c r="N14" s="1">
-        <v>0.1430861723446894</v>
-      </c>
-      <c r="O14" s="1">
-        <v>1.7772421994397172</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="R14" s="1">
-        <v>1.62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B15" s="1">
         <v>2</v>
       </c>
+      <c r="C15" s="1">
+        <v>1.4133474668067691E-3</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2.8853393323793255</v>
+      </c>
       <c r="E15" s="1">
         <v>0.13911993692717059</v>
       </c>
@@ -3695,29 +5312,20 @@
       <c r="H15" s="1">
         <v>0.13297332509443671</v>
       </c>
-      <c r="K15" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L15" s="2">
-        <v>56</v>
-      </c>
-      <c r="M15" s="1">
-        <v>1.484014840148264E-3</v>
-      </c>
-      <c r="N15" s="1">
-        <v>0.17279256442754556</v>
-      </c>
-      <c r="O15" s="1">
-        <v>1.6951263354634258</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B16" s="1">
         <v>2</v>
       </c>
+      <c r="C16" s="1">
+        <v>1.5250152501528429E-3</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1.9067806955784921</v>
+      </c>
       <c r="E16" s="1">
         <v>0.13911993692717059</v>
       </c>
@@ -3730,29 +5338,20 @@
       <c r="H16" s="1">
         <v>0.15578764142732804</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L16" s="2">
-        <v>56</v>
-      </c>
-      <c r="M16" s="1">
-        <v>1.5760157601505359E-3</v>
-      </c>
-      <c r="N16" s="1">
-        <v>0.1863437537080784</v>
-      </c>
-      <c r="O16" s="1">
-        <v>1.6321784584194605</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B17" s="1">
         <v>2</v>
       </c>
+      <c r="C17" s="1">
+        <v>1.4550145501450729E-3</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2.254059142722955</v>
+      </c>
       <c r="E17" s="1">
         <v>0.13911993692717059</v>
       </c>
@@ -3764,89 +5363,6 @@
       </c>
       <c r="H17" s="1">
         <v>0.16935064935064942</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L17" s="2">
-        <v>25</v>
-      </c>
-      <c r="M17" s="1">
-        <v>1.686016860168494E-3</v>
-      </c>
-      <c r="N17" s="1">
-        <v>0.16556028504471754</v>
-      </c>
-      <c r="O17" s="1">
-        <v>1.6090048691339709</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="K18" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="L18" s="2">
-        <v>25</v>
-      </c>
-      <c r="M18" s="1">
-        <v>1.9700197001942142E-3</v>
-      </c>
-      <c r="N18" s="1">
-        <v>0.19470446643487566</v>
-      </c>
-      <c r="O18" s="1">
-        <v>1.6060302554528956</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="K19" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L19" s="2">
-        <v>25</v>
-      </c>
-      <c r="M19" s="1">
-        <v>1.4060140601390699E-3</v>
-      </c>
-      <c r="N19" s="1">
-        <v>0.13297332509443671</v>
-      </c>
-      <c r="O19" s="1">
-        <v>1.6867190368361413</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="K20" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L20" s="2">
-        <v>25</v>
-      </c>
-      <c r="M20" s="1">
-        <v>1.516015160152762E-3</v>
-      </c>
-      <c r="N20" s="1">
-        <v>0.15578764142732804</v>
-      </c>
-      <c r="O20" s="1">
-        <v>1.678484887889131</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="K21" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="L21" s="2">
-        <v>25</v>
-      </c>
-      <c r="M21" s="1">
-        <v>1.455014550145075E-3</v>
-      </c>
-      <c r="N21" s="1">
-        <v>0.16935064935064942</v>
-      </c>
-      <c r="O21" s="1">
-        <v>1.601954608561813</v>
       </c>
     </row>
   </sheetData>
@@ -3858,19 +5374,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDBDB9C2-512F-468A-9E95-0283D0C33914}">
   <dimension ref="B2:C33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="13.265625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B2" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" s="18"/>
+      <c r="B2" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="12"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B3" s="6" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.45">
@@ -3938,25 +5457,25 @@
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
     </row>
     <row r="13" spans="2:3" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B13" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" s="18"/>
+      <c r="B13" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="12"/>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B14" s="6" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B15" s="6">
+      <c r="B15" s="13">
         <v>10000000</v>
       </c>
       <c r="C15" s="6">
@@ -3964,7 +5483,7 @@
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B16" s="6">
+      <c r="B16" s="13">
         <v>40000000</v>
       </c>
       <c r="C16" s="6">
@@ -3972,7 +5491,7 @@
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B17" s="6">
+      <c r="B17" s="13">
         <v>100000000</v>
       </c>
       <c r="C17" s="6">
@@ -3980,7 +5499,7 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B18" s="6">
+      <c r="B18" s="13">
         <v>200000000</v>
       </c>
       <c r="C18" s="6">
@@ -3988,7 +5507,7 @@
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B19" s="6">
+      <c r="B19" s="13">
         <v>300000000</v>
       </c>
       <c r="C19" s="6">
@@ -3996,7 +5515,7 @@
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B20" s="6">
+      <c r="B20" s="13">
         <v>500000000</v>
       </c>
       <c r="C20" s="6">
@@ -4004,7 +5523,7 @@
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B21" s="6">
+      <c r="B21" s="13">
         <v>700000000</v>
       </c>
       <c r="C21" s="6">
@@ -4012,7 +5531,7 @@
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B22" s="6">
+      <c r="B22" s="13">
         <v>1000000000</v>
       </c>
       <c r="C22" s="6">
@@ -4020,21 +5539,21 @@
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
     </row>
     <row r="24" spans="2:3" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B24" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="18"/>
+      <c r="B24" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="12"/>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B25" s="6" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.45">
@@ -4108,5 +5627,6 @@
     <mergeCell ref="B24:C24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>